--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1250000/Output_2_10.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1250000/Output_2_10.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>268974.3716841202</v>
+        <v>271171.4946176034</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4964010.941928677</v>
+        <v>4968231.017992428</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22285259.10284261</v>
+        <v>22289395.19939269</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4042825.87678395</v>
+        <v>4041050.861125655</v>
       </c>
     </row>
     <row r="11">
@@ -2074,25 +2074,25 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>40</v>
+        <v>12.92549025883184</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2131,13 +2131,13 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="21">
@@ -2153,22 +2153,22 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2198,19 +2198,19 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2235,25 +2235,25 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>9.977552361264268</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2286,13 +2286,13 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2323,13 +2323,13 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>22.91618947337665</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2353,13 +2353,13 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="S23" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="T23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2368,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -2393,13 +2393,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2441,19 +2441,19 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="25">
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2487,10 +2487,10 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>27.291937497222</v>
       </c>
       <c r="K25" t="n">
-        <v>6.415584701379575</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2505,16 +2505,16 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="26">
@@ -2557,10 +2557,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="H26" t="n">
-        <v>40</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2593,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="27">
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -2630,16 +2630,16 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="G27" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2681,16 +2681,16 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2748,16 +2748,16 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>9.137025436486075</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="S28" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="T28" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="U28" t="n">
-        <v>40</v>
+        <v>9.977552361264268</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2779,22 +2779,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>40</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="30">
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>40</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -2870,13 +2870,13 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2915,13 +2915,13 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -2952,19 +2952,19 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>26.86753361060322</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="K31" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2982,10 +2982,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>9.977552361264268</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>24.87477961344436</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -3061,16 +3061,16 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3079,13 +3079,13 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="X32" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="33">
@@ -3098,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -3143,22 +3143,22 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="S33" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="W33" t="n">
-        <v>40</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>9.977552361264271</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -3183,16 +3183,16 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3237,13 +3237,13 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="35">
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -3265,16 +3265,16 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3298,13 +3298,13 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -3316,10 +3316,10 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>25.24130078545516</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3332,13 +3332,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="C36" t="n">
-        <v>35.23199999999997</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3353,7 +3353,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3383,19 +3383,19 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -3453,19 +3453,19 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>40</v>
+        <v>9.977552361264268</v>
       </c>
       <c r="R37" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="S37" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="T37" t="n">
-        <v>6.415584701379575</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>24.87477961344436</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -3511,10 +3511,10 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>23.28271064538745</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3535,10 +3535,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3547,19 +3547,19 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="39">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>34.48540867374211</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3620,25 +3620,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="40">
@@ -3654,16 +3654,16 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>6.415584701379572</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="E40" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="F40" t="n">
-        <v>40</v>
+        <v>9.977552361264268</v>
       </c>
       <c r="G40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="C41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3739,13 +3739,13 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>25.24130078545516</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3784,13 +3784,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>24.87477961344436</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -3824,10 +3824,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3854,22 +3854,22 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -3885,19 +3885,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>40</v>
+        <v>24.5704967621155</v>
       </c>
       <c r="F43" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3912,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3927,7 +3927,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3945,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>160</v>
+        <v>68.2764642733967</v>
       </c>
       <c r="C20" t="n">
-        <v>160</v>
+        <v>68.2764642733967</v>
       </c>
       <c r="D20" t="n">
-        <v>124.4121212121212</v>
+        <v>68.2764642733967</v>
       </c>
       <c r="E20" t="n">
-        <v>84.00808080808082</v>
+        <v>68.2764642733967</v>
       </c>
       <c r="F20" t="n">
-        <v>43.60404040404041</v>
+        <v>68.2764642733967</v>
       </c>
       <c r="G20" t="n">
-        <v>3.2</v>
+        <v>55.22041350689989</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>15.2366994040306</v>
       </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>15.2366994040306</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K20" t="n">
-        <v>42.8</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L20" t="n">
-        <v>42.8</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="M20" t="n">
-        <v>82.40000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="N20" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="O20" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="P20" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q20" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="R20" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="S20" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="T20" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="U20" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="V20" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="W20" t="n">
-        <v>160</v>
+        <v>108.260178376266</v>
       </c>
       <c r="X20" t="n">
-        <v>160</v>
+        <v>108.260178376266</v>
       </c>
       <c r="Y20" t="n">
-        <v>160</v>
+        <v>68.2764642733967</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>160</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="C21" t="n">
-        <v>160</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="D21" t="n">
-        <v>160</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E21" t="n">
-        <v>160</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F21" t="n">
-        <v>124.4121212121212</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G21" t="n">
-        <v>84.00808080808082</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H21" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K21" t="n">
-        <v>42.8</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="L21" t="n">
-        <v>42.8</v>
+        <v>81.54278654139161</v>
       </c>
       <c r="M21" t="n">
-        <v>42.8</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="N21" t="n">
-        <v>42.8</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="O21" t="n">
-        <v>80.80000000000001</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P21" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="Q21" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R21" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S21" t="n">
-        <v>160</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="T21" t="n">
-        <v>160</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="U21" t="n">
-        <v>160</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="V21" t="n">
-        <v>160</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="W21" t="n">
-        <v>160</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="X21" t="n">
-        <v>160</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="Y21" t="n">
-        <v>160</v>
+        <v>38.38436553875449</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>160</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="C22" t="n">
-        <v>160</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="D22" t="n">
-        <v>160</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="E22" t="n">
-        <v>160</v>
+        <v>13.245045875396</v>
       </c>
       <c r="F22" t="n">
-        <v>160</v>
+        <v>13.245045875396</v>
       </c>
       <c r="G22" t="n">
-        <v>150.7706813772868</v>
+        <v>13.245045875396</v>
       </c>
       <c r="H22" t="n">
-        <v>110.3666409732464</v>
+        <v>13.245045875396</v>
       </c>
       <c r="I22" t="n">
-        <v>69.96260056920597</v>
+        <v>13.245045875396</v>
       </c>
       <c r="J22" t="n">
-        <v>29.55856016516557</v>
+        <v>13.245045875396</v>
       </c>
       <c r="K22" t="n">
-        <v>29.55856016516557</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L22" t="n">
-        <v>56.87268517287855</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M22" t="n">
-        <v>96.06072336510073</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N22" t="n">
-        <v>135.6607233651007</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Q22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="R22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="S22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="T22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="U22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="V22" t="n">
-        <v>160</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="W22" t="n">
-        <v>160</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="X22" t="n">
-        <v>160</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="Y22" t="n">
-        <v>160</v>
+        <v>53.22875997826529</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.2</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="C23" t="n">
-        <v>3.2</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="D23" t="n">
-        <v>3.2</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="E23" t="n">
-        <v>3.2</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="F23" t="n">
-        <v>3.2</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="G23" t="n">
-        <v>3.2</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2</v>
+        <v>55.22041350689989</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>15.2366994040306</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L23" t="n">
-        <v>42.8</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="M23" t="n">
-        <v>80.80000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="N23" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="O23" t="n">
-        <v>160</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P23" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q23" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R23" t="n">
-        <v>119.5959595959596</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="S23" t="n">
-        <v>79.19191919191917</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="T23" t="n">
-        <v>38.78787878787876</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="U23" t="n">
-        <v>38.78787878787876</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="V23" t="n">
-        <v>38.78787878787876</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="W23" t="n">
-        <v>3.2</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="X23" t="n">
-        <v>3.2</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.2</v>
+        <v>78.36807964162378</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>43.60404040404041</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="C24" t="n">
-        <v>43.60404040404041</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="D24" t="n">
-        <v>43.60404040404041</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="E24" t="n">
-        <v>3.2</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="G24" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H24" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K24" t="n">
-        <v>41.20000000000001</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L24" t="n">
-        <v>41.20000000000001</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="M24" t="n">
-        <v>80.80000000000001</v>
+        <v>81.54278654139161</v>
       </c>
       <c r="N24" t="n">
-        <v>80.80000000000001</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="O24" t="n">
-        <v>80.80000000000001</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P24" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q24" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R24" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S24" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T24" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U24" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="V24" t="n">
-        <v>84.00808080808082</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="W24" t="n">
-        <v>43.60404040404041</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="X24" t="n">
-        <v>43.60404040404041</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="Y24" t="n">
-        <v>43.60404040404041</v>
+        <v>78.36807964162378</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.680388587252096</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="C25" t="n">
-        <v>9.680388587252096</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="D25" t="n">
-        <v>9.680388587252096</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="E25" t="n">
-        <v>9.680388587252096</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="F25" t="n">
-        <v>9.680388587252096</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="G25" t="n">
-        <v>9.680388587252096</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="H25" t="n">
-        <v>9.680388587252096</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="I25" t="n">
-        <v>9.680388587252096</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="J25" t="n">
-        <v>9.680388587252096</v>
+        <v>25.66114634470771</v>
       </c>
       <c r="K25" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L25" t="n">
-        <v>30.51412500771298</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M25" t="n">
-        <v>69.70216319993516</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N25" t="n">
-        <v>109.3021631999352</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O25" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P25" t="n">
-        <v>130.8925097993733</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Q25" t="n">
-        <v>90.48846939533291</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="R25" t="n">
-        <v>50.0844289912925</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="S25" t="n">
-        <v>9.680388587252096</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="T25" t="n">
-        <v>9.680388587252096</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="U25" t="n">
-        <v>9.680388587252096</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="V25" t="n">
-        <v>9.680388587252096</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="W25" t="n">
-        <v>9.680388587252096</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="X25" t="n">
-        <v>9.680388587252096</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Y25" t="n">
-        <v>9.680388587252096</v>
+        <v>93.21247408113457</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>84.00808080808082</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="C26" t="n">
-        <v>84.00808080808082</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="D26" t="n">
-        <v>84.00808080808082</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="E26" t="n">
-        <v>84.00808080808082</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="F26" t="n">
-        <v>84.00808080808082</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="G26" t="n">
-        <v>43.60404040404041</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="H26" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J26" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K26" t="n">
-        <v>42.8</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="L26" t="n">
-        <v>82.40000000000001</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="M26" t="n">
-        <v>120.4</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="N26" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="O26" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="P26" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q26" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R26" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S26" t="n">
-        <v>119.5959595959596</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="T26" t="n">
-        <v>119.5959595959596</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="U26" t="n">
-        <v>119.5959595959596</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="V26" t="n">
-        <v>84.00808080808082</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="W26" t="n">
-        <v>84.00808080808082</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="X26" t="n">
-        <v>84.00808080808082</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="Y26" t="n">
-        <v>84.00808080808082</v>
+        <v>78.36807964162378</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>79.19191919191917</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="C27" t="n">
-        <v>79.19191919191917</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="D27" t="n">
-        <v>79.19191919191917</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="E27" t="n">
-        <v>79.19191919191917</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="F27" t="n">
-        <v>79.19191919191917</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G27" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I27" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K27" t="n">
-        <v>41.20000000000001</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L27" t="n">
-        <v>41.20000000000001</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="M27" t="n">
-        <v>41.20000000000001</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="N27" t="n">
-        <v>80.80000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O27" t="n">
-        <v>80.80000000000001</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P27" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q27" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R27" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S27" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T27" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U27" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="V27" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="W27" t="n">
-        <v>119.5959595959596</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="X27" t="n">
-        <v>119.5959595959596</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="Y27" t="n">
-        <v>79.19191919191917</v>
+        <v>118.3517937444931</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="C28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="D28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L28" t="n">
-        <v>30.51412500771298</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M28" t="n">
-        <v>69.70216319993516</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N28" t="n">
-        <v>109.3021631999352</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O28" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P28" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Q28" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="R28" t="n">
-        <v>124.4121212121212</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="S28" t="n">
-        <v>84.00808080808082</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="T28" t="n">
-        <v>43.60404040404041</v>
+        <v>13.245045875396</v>
       </c>
       <c r="U28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="V28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="W28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="X28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="Y28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>119.5959595959596</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="C29" t="n">
-        <v>119.5959595959596</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="D29" t="n">
-        <v>84.00808080808082</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="E29" t="n">
-        <v>43.60404040404041</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="F29" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="G29" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H29" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I29" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J29" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K29" t="n">
-        <v>3.2</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="L29" t="n">
-        <v>42.8</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="M29" t="n">
-        <v>82.40000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="N29" t="n">
-        <v>122</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="O29" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="P29" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q29" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R29" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S29" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T29" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U29" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="V29" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="W29" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="X29" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Y29" t="n">
-        <v>119.5959595959596</v>
+        <v>118.3517937444931</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.2</v>
+        <v>123.1178524655551</v>
       </c>
       <c r="C30" t="n">
-        <v>3.2</v>
+        <v>123.1178524655551</v>
       </c>
       <c r="D30" t="n">
-        <v>3.2</v>
+        <v>123.1178524655551</v>
       </c>
       <c r="E30" t="n">
-        <v>3.2</v>
+        <v>123.1178524655551</v>
       </c>
       <c r="F30" t="n">
-        <v>3.2</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="G30" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="H30" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I30" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J30" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K30" t="n">
-        <v>3.2</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="L30" t="n">
-        <v>42.8</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="M30" t="n">
-        <v>82.40000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="N30" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="O30" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P30" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q30" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R30" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S30" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T30" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U30" t="n">
-        <v>124.4121212121212</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="V30" t="n">
-        <v>84.00808080808082</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="W30" t="n">
-        <v>43.60404040404041</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="X30" t="n">
-        <v>43.60404040404041</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Y30" t="n">
-        <v>43.60404040404041</v>
+        <v>158.3355078473624</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>133.6414398348344</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="C31" t="n">
-        <v>133.6414398348344</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="D31" t="n">
-        <v>133.6414398348344</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="E31" t="n">
-        <v>133.6414398348344</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="F31" t="n">
-        <v>133.6414398348344</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="G31" t="n">
-        <v>106.5025169958413</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="H31" t="n">
-        <v>66.09847659180087</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="I31" t="n">
-        <v>66.09847659180087</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="J31" t="n">
-        <v>25.69443618776046</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K31" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L31" t="n">
-        <v>30.51412500771298</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M31" t="n">
-        <v>69.70216319993516</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N31" t="n">
-        <v>109.3021631999352</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O31" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P31" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Q31" t="n">
-        <v>133.6414398348344</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="R31" t="n">
-        <v>133.6414398348344</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="S31" t="n">
-        <v>133.6414398348344</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="T31" t="n">
-        <v>133.6414398348344</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="U31" t="n">
-        <v>133.6414398348344</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="V31" t="n">
-        <v>133.6414398348344</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="W31" t="n">
-        <v>133.6414398348344</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="X31" t="n">
-        <v>133.6414398348344</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="Y31" t="n">
-        <v>133.6414398348344</v>
+        <v>43.15042425981653</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="C32" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="D32" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E32" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F32" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G32" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H32" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I32" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J32" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K32" t="n">
-        <v>3.2</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="L32" t="n">
-        <v>41.20000000000001</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="M32" t="n">
-        <v>80.80000000000001</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="N32" t="n">
-        <v>120.4</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O32" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P32" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q32" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="R32" t="n">
-        <v>119.5959595959596</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="S32" t="n">
-        <v>119.5959595959596</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="T32" t="n">
-        <v>79.19191919191917</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="U32" t="n">
-        <v>79.19191919191917</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="V32" t="n">
-        <v>79.19191919191917</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="W32" t="n">
-        <v>79.19191919191917</v>
+        <v>108.260178376266</v>
       </c>
       <c r="X32" t="n">
-        <v>43.60404040404041</v>
+        <v>108.260178376266</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.2</v>
+        <v>68.2764642733967</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="C33" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="D33" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E33" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F33" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G33" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H33" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J33" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K33" t="n">
-        <v>3.2</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="L33" t="n">
-        <v>42.8</v>
+        <v>81.54278654139161</v>
       </c>
       <c r="M33" t="n">
-        <v>42.8</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="N33" t="n">
-        <v>42.8</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="O33" t="n">
-        <v>80.80000000000001</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P33" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q33" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R33" t="n">
-        <v>160</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="S33" t="n">
-        <v>119.5959595959596</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="T33" t="n">
-        <v>119.5959595959596</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="U33" t="n">
-        <v>79.19191919191917</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="V33" t="n">
-        <v>79.19191919191917</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="W33" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="X33" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="Y33" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>160</v>
+        <v>28.30602982030574</v>
       </c>
       <c r="C34" t="n">
-        <v>160</v>
+        <v>28.30602982030574</v>
       </c>
       <c r="D34" t="n">
-        <v>160</v>
+        <v>28.30602982030574</v>
       </c>
       <c r="E34" t="n">
-        <v>150.7706813772868</v>
+        <v>28.30602982030574</v>
       </c>
       <c r="F34" t="n">
-        <v>110.3666409732464</v>
+        <v>28.30602982030574</v>
       </c>
       <c r="G34" t="n">
-        <v>69.96260056920597</v>
+        <v>28.30602982030574</v>
       </c>
       <c r="H34" t="n">
-        <v>29.55856016516557</v>
+        <v>28.30602982030574</v>
       </c>
       <c r="I34" t="n">
-        <v>29.55856016516557</v>
+        <v>28.30602982030574</v>
       </c>
       <c r="J34" t="n">
-        <v>29.55856016516557</v>
+        <v>28.30602982030574</v>
       </c>
       <c r="K34" t="n">
-        <v>29.55856016516557</v>
+        <v>28.30602982030574</v>
       </c>
       <c r="L34" t="n">
-        <v>56.87268517287855</v>
+        <v>55.62015482801871</v>
       </c>
       <c r="M34" t="n">
-        <v>96.06072336510073</v>
+        <v>94.80819302024089</v>
       </c>
       <c r="N34" t="n">
-        <v>135.6607233651007</v>
+        <v>133.9962312124631</v>
       </c>
       <c r="O34" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="P34" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q34" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R34" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S34" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T34" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U34" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="V34" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="W34" t="n">
-        <v>160</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="X34" t="n">
-        <v>160</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="Y34" t="n">
-        <v>160</v>
+        <v>38.38436553875449</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>84.00808080808082</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="C35" t="n">
-        <v>84.00808080808082</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="D35" t="n">
-        <v>84.00808080808082</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="E35" t="n">
-        <v>84.00808080808082</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="F35" t="n">
-        <v>84.00808080808082</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G35" t="n">
-        <v>84.00808080808082</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H35" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I35" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J35" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K35" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L35" t="n">
-        <v>41.20000000000001</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="M35" t="n">
-        <v>80.80000000000001</v>
+        <v>81.54278654139161</v>
       </c>
       <c r="N35" t="n">
-        <v>120.4</v>
+        <v>120.7308247336138</v>
       </c>
       <c r="O35" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="P35" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q35" t="n">
-        <v>149.9083846317729</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R35" t="n">
-        <v>149.9083846317729</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S35" t="n">
-        <v>149.9083846317729</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="T35" t="n">
-        <v>149.9083846317729</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="U35" t="n">
-        <v>149.9083846317729</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="V35" t="n">
-        <v>149.9083846317729</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="W35" t="n">
-        <v>109.5043442277325</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="X35" t="n">
-        <v>84.00808080808082</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="Y35" t="n">
-        <v>84.00808080808082</v>
+        <v>118.3517937444931</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>38.78787878787876</v>
+        <v>123.1178524655551</v>
       </c>
       <c r="C36" t="n">
-        <v>3.2</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="D36" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="E36" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="F36" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="G36" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="H36" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="I36" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J36" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K36" t="n">
-        <v>41.20000000000001</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L36" t="n">
-        <v>41.20000000000001</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="M36" t="n">
-        <v>41.20000000000001</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="N36" t="n">
-        <v>41.20000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O36" t="n">
-        <v>80.80000000000001</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P36" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q36" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R36" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S36" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T36" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U36" t="n">
-        <v>79.19191919191917</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="V36" t="n">
-        <v>79.19191919191917</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="W36" t="n">
-        <v>38.78787878787876</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="X36" t="n">
-        <v>38.78787878787876</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Y36" t="n">
-        <v>38.78787878787876</v>
+        <v>158.3355078473624</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="C37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="D37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L37" t="n">
-        <v>30.51412500771298</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M37" t="n">
-        <v>69.70216319993516</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N37" t="n">
-        <v>109.3021631999352</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O37" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P37" t="n">
-        <v>130.8925097993733</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Q37" t="n">
-        <v>90.48846939533291</v>
+        <v>123.1178524655551</v>
       </c>
       <c r="R37" t="n">
-        <v>50.0844289912925</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="S37" t="n">
-        <v>9.680388587252096</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="T37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="U37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="V37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="W37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="X37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>38.78787878787876</v>
+        <v>28.29275017052741</v>
       </c>
       <c r="C38" t="n">
-        <v>38.78787878787876</v>
+        <v>28.29275017052741</v>
       </c>
       <c r="D38" t="n">
-        <v>38.78787878787876</v>
+        <v>28.29275017052741</v>
       </c>
       <c r="E38" t="n">
-        <v>38.78787878787876</v>
+        <v>28.29275017052741</v>
       </c>
       <c r="F38" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G38" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H38" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I38" t="n">
-        <v>15.26998924708335</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K38" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L38" t="n">
-        <v>42.8</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="M38" t="n">
-        <v>82.40000000000001</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="N38" t="n">
-        <v>122</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O38" t="n">
-        <v>160</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P38" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q38" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="R38" t="n">
-        <v>160</v>
+        <v>108.260178376266</v>
       </c>
       <c r="S38" t="n">
-        <v>160</v>
+        <v>108.260178376266</v>
       </c>
       <c r="T38" t="n">
-        <v>160</v>
+        <v>108.260178376266</v>
       </c>
       <c r="U38" t="n">
-        <v>119.5959595959596</v>
+        <v>108.260178376266</v>
       </c>
       <c r="V38" t="n">
-        <v>79.19191919191917</v>
+        <v>108.260178376266</v>
       </c>
       <c r="W38" t="n">
-        <v>38.78787878787876</v>
+        <v>108.260178376266</v>
       </c>
       <c r="X38" t="n">
-        <v>38.78787878787876</v>
+        <v>108.260178376266</v>
       </c>
       <c r="Y38" t="n">
-        <v>38.78787878787876</v>
+        <v>68.2764642733967</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.954132652785714</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="C39" t="n">
-        <v>3.954132652785714</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="D39" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E39" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F39" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G39" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H39" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I39" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J39" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K39" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L39" t="n">
-        <v>41.20000000000001</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="M39" t="n">
-        <v>41.20000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="N39" t="n">
-        <v>80.80000000000001</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="O39" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="P39" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q39" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R39" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S39" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T39" t="n">
-        <v>79.19191919191917</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U39" t="n">
-        <v>79.19191919191917</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="V39" t="n">
-        <v>79.19191919191917</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="W39" t="n">
-        <v>79.19191919191917</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="X39" t="n">
-        <v>79.19191919191917</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.78787878787876</v>
+        <v>38.38436553875449</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>130.8925097993733</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="C40" t="n">
-        <v>130.8925097993733</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="D40" t="n">
-        <v>124.4121212121212</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="E40" t="n">
-        <v>84.00808080808082</v>
+        <v>13.245045875396</v>
       </c>
       <c r="F40" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G40" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H40" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I40" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J40" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K40" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L40" t="n">
-        <v>30.51412500771298</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M40" t="n">
-        <v>69.70216319993516</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N40" t="n">
-        <v>109.3021631999352</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O40" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P40" t="n">
-        <v>130.8925097993733</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Q40" t="n">
-        <v>130.8925097993733</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="R40" t="n">
-        <v>130.8925097993733</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="S40" t="n">
-        <v>130.8925097993733</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="T40" t="n">
-        <v>130.8925097993733</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="U40" t="n">
-        <v>130.8925097993733</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="V40" t="n">
-        <v>130.8925097993733</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="W40" t="n">
-        <v>130.8925097993733</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="X40" t="n">
-        <v>130.8925097993733</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="Y40" t="n">
-        <v>130.8925097993733</v>
+        <v>93.21247408113457</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>69.10030382369209</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="C41" t="n">
-        <v>28.69626341965168</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="D41" t="n">
-        <v>28.69626341965168</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="E41" t="n">
-        <v>28.69626341965168</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="F41" t="n">
-        <v>3.2</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="G41" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="H41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L41" t="n">
-        <v>42.8</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="M41" t="n">
-        <v>82.40000000000001</v>
+        <v>81.54278654139161</v>
       </c>
       <c r="N41" t="n">
-        <v>122</v>
+        <v>81.54278654139161</v>
       </c>
       <c r="O41" t="n">
-        <v>160</v>
+        <v>120.7308247336138</v>
       </c>
       <c r="P41" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q41" t="n">
-        <v>149.9083846317729</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="R41" t="n">
-        <v>149.9083846317729</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="S41" t="n">
-        <v>149.9083846317729</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="T41" t="n">
-        <v>149.9083846317729</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="U41" t="n">
-        <v>109.5043442277325</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="V41" t="n">
-        <v>69.10030382369209</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="W41" t="n">
-        <v>69.10030382369209</v>
+        <v>123.1178524655551</v>
       </c>
       <c r="X41" t="n">
-        <v>69.10030382369209</v>
+        <v>123.1178524655551</v>
       </c>
       <c r="Y41" t="n">
-        <v>69.10030382369209</v>
+        <v>123.1178524655551</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>119.5959595959596</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="C42" t="n">
-        <v>79.19191919191917</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="D42" t="n">
-        <v>79.19191919191917</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E42" t="n">
-        <v>79.19191919191917</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F42" t="n">
-        <v>79.19191919191917</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G42" t="n">
-        <v>79.19191919191917</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H42" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="M42" t="n">
-        <v>3.2</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="N42" t="n">
-        <v>41.20000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O42" t="n">
-        <v>80.80000000000001</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P42" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q42" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R42" t="n">
-        <v>160</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="S42" t="n">
-        <v>160</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="T42" t="n">
-        <v>160</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="U42" t="n">
-        <v>160</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="V42" t="n">
-        <v>160</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="W42" t="n">
-        <v>160</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="X42" t="n">
-        <v>160</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="Y42" t="n">
-        <v>160</v>
+        <v>3.166710156947247</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>93.23739943079403</v>
+        <v>90.46354404567346</v>
       </c>
       <c r="C43" t="n">
-        <v>93.23739943079403</v>
+        <v>90.46354404567346</v>
       </c>
       <c r="D43" t="n">
-        <v>84.00808080808082</v>
+        <v>90.46354404567346</v>
       </c>
       <c r="E43" t="n">
-        <v>43.60404040404041</v>
+        <v>65.64486044757699</v>
       </c>
       <c r="F43" t="n">
-        <v>3.2</v>
+        <v>25.66114634470771</v>
       </c>
       <c r="G43" t="n">
-        <v>3.2</v>
+        <v>25.66114634470771</v>
       </c>
       <c r="H43" t="n">
-        <v>3.2</v>
+        <v>25.66114634470771</v>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>25.66114634470771</v>
       </c>
       <c r="J43" t="n">
-        <v>3.2</v>
+        <v>25.66114634470771</v>
       </c>
       <c r="K43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L43" t="n">
-        <v>30.51412500771298</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M43" t="n">
-        <v>69.70216319993516</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N43" t="n">
-        <v>109.3021631999352</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O43" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P43" t="n">
-        <v>133.6414398348344</v>
+        <v>130.4472581485427</v>
       </c>
       <c r="Q43" t="n">
-        <v>133.6414398348344</v>
+        <v>130.4472581485427</v>
       </c>
       <c r="R43" t="n">
-        <v>133.6414398348344</v>
+        <v>130.4472581485427</v>
       </c>
       <c r="S43" t="n">
-        <v>133.6414398348344</v>
+        <v>130.4472581485427</v>
       </c>
       <c r="T43" t="n">
-        <v>133.6414398348344</v>
+        <v>130.4472581485427</v>
       </c>
       <c r="U43" t="n">
-        <v>133.6414398348344</v>
+        <v>130.4472581485427</v>
       </c>
       <c r="V43" t="n">
-        <v>133.6414398348344</v>
+        <v>90.46354404567346</v>
       </c>
       <c r="W43" t="n">
-        <v>133.6414398348344</v>
+        <v>90.46354404567346</v>
       </c>
       <c r="X43" t="n">
-        <v>133.6414398348344</v>
+        <v>90.46354404567346</v>
       </c>
       <c r="Y43" t="n">
-        <v>133.6414398348344</v>
+        <v>90.46354404567346</v>
       </c>
     </row>
     <row r="44">
@@ -9381,19 +9381,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>260.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L20" t="n">
-        <v>235.7664149699872</v>
+        <v>273.750943367713</v>
       </c>
       <c r="M20" t="n">
-        <v>270.3462332272727</v>
+        <v>269.9301101891133</v>
       </c>
       <c r="N20" t="n">
-        <v>267.7969019804293</v>
+        <v>268.9969405584315</v>
       </c>
       <c r="O20" t="n">
-        <v>270.0982114216868</v>
+        <v>269.6820883835273</v>
       </c>
       <c r="P20" t="n">
         <v>231.2329957552695</v>
@@ -9460,25 +9460,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>177.841438974359</v>
+        <v>177.4253159361996</v>
       </c>
       <c r="L21" t="n">
-        <v>138.5543797798742</v>
+        <v>178.1382567417148</v>
       </c>
       <c r="M21" t="n">
-        <v>142.1340339220183</v>
+        <v>180.1185623197441</v>
       </c>
       <c r="N21" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>180.9800828282828</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>173.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
-        <v>179.9817740860215</v>
+        <v>179.5656510478621</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9548,7 +9548,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N22" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O22" t="n">
         <v>163.0416663658825</v>
@@ -9621,19 +9621,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L23" t="n">
-        <v>275.7664149699872</v>
+        <v>273.750943367713</v>
       </c>
       <c r="M23" t="n">
-        <v>268.7300716111112</v>
+        <v>269.9301101891133</v>
       </c>
       <c r="N23" t="n">
-        <v>269.4130635965909</v>
+        <v>268.9969405584315</v>
       </c>
       <c r="O23" t="n">
-        <v>270.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P23" t="n">
-        <v>231.2329957552695</v>
+        <v>270.8168727171101</v>
       </c>
       <c r="Q23" t="n">
         <v>212.3149906599047</v>
@@ -9697,25 +9697,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>176.2252773581974</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>138.5543797798742</v>
+        <v>178.1382567417148</v>
       </c>
       <c r="M24" t="n">
-        <v>182.1340339220183</v>
+        <v>181.7179108838589</v>
       </c>
       <c r="N24" t="n">
-        <v>131.3417120833333</v>
+        <v>169.3262404810591</v>
       </c>
       <c r="O24" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>173.9744074143302</v>
+        <v>173.5582843761708</v>
       </c>
       <c r="Q24" t="n">
-        <v>179.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9785,7 +9785,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N25" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O25" t="n">
         <v>163.0416663658825</v>
@@ -9855,19 +9855,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>260.0898510449805</v>
+        <v>258.0743794427063</v>
       </c>
       <c r="L26" t="n">
-        <v>275.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M26" t="n">
-        <v>268.7300716111111</v>
+        <v>269.9301101891133</v>
       </c>
       <c r="N26" t="n">
-        <v>229.4130635965909</v>
+        <v>268.9969405584315</v>
       </c>
       <c r="O26" t="n">
-        <v>270.0982114216868</v>
+        <v>269.6820883835273</v>
       </c>
       <c r="P26" t="n">
         <v>231.2329957552695</v>
@@ -9934,25 +9934,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>176.2252773581974</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
-        <v>138.5543797798742</v>
+        <v>176.5389081776</v>
       </c>
       <c r="M27" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N27" t="n">
-        <v>171.3417120833333</v>
+        <v>170.9255890451739</v>
       </c>
       <c r="O27" t="n">
-        <v>142.5962444444444</v>
+        <v>182.180121406285</v>
       </c>
       <c r="P27" t="n">
-        <v>173.9744074143302</v>
+        <v>173.5582843761708</v>
       </c>
       <c r="Q27" t="n">
-        <v>179.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10022,7 +10022,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N28" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O28" t="n">
         <v>163.0416663658825</v>
@@ -10092,19 +10092,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>220.0898510449805</v>
+        <v>258.0743794427063</v>
       </c>
       <c r="L29" t="n">
-        <v>275.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M29" t="n">
-        <v>270.3462332272727</v>
+        <v>269.9301101891133</v>
       </c>
       <c r="N29" t="n">
-        <v>269.4130635965909</v>
+        <v>268.9969405584315</v>
       </c>
       <c r="O29" t="n">
-        <v>268.4820498055251</v>
+        <v>269.6820883835273</v>
       </c>
       <c r="P29" t="n">
         <v>231.2329957552695</v>
@@ -10171,25 +10171,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>137.841438974359</v>
+        <v>177.4253159361996</v>
       </c>
       <c r="L30" t="n">
-        <v>178.5543797798742</v>
+        <v>176.5389081776</v>
       </c>
       <c r="M30" t="n">
-        <v>182.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
-        <v>169.7255504671717</v>
+        <v>170.9255890451739</v>
       </c>
       <c r="O30" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
-        <v>133.9744074143302</v>
+        <v>173.5582843761708</v>
       </c>
       <c r="Q30" t="n">
-        <v>179.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10259,7 +10259,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N31" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O31" t="n">
         <v>163.0416663658825</v>
@@ -10329,22 +10329,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>220.0898510449805</v>
+        <v>259.6737280068211</v>
       </c>
       <c r="L32" t="n">
-        <v>274.1502533538256</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M32" t="n">
-        <v>270.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N32" t="n">
-        <v>269.4130635965909</v>
+        <v>267.3975919943167</v>
       </c>
       <c r="O32" t="n">
-        <v>230.0982114216867</v>
+        <v>269.6820883835273</v>
       </c>
       <c r="P32" t="n">
-        <v>271.2329957552695</v>
+        <v>270.8168727171101</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10408,25 +10408,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>137.841438974359</v>
+        <v>177.4253159361996</v>
       </c>
       <c r="L33" t="n">
-        <v>178.5543797798742</v>
+        <v>178.1382567417148</v>
       </c>
       <c r="M33" t="n">
-        <v>142.1340339220183</v>
+        <v>180.1185623197441</v>
       </c>
       <c r="N33" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>180.9800828282828</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>173.9744074143302</v>
+        <v>173.5582843761708</v>
       </c>
       <c r="Q33" t="n">
-        <v>179.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10496,7 +10496,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N34" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O34" t="n">
         <v>163.0416663658825</v>
@@ -10569,19 +10569,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L35" t="n">
-        <v>274.1502533538256</v>
+        <v>275.3502919318278</v>
       </c>
       <c r="M35" t="n">
-        <v>270.3462332272727</v>
+        <v>269.9301101891133</v>
       </c>
       <c r="N35" t="n">
-        <v>269.4130635965909</v>
+        <v>268.9969405584315</v>
       </c>
       <c r="O35" t="n">
-        <v>230.0982114216867</v>
+        <v>268.0827398194126</v>
       </c>
       <c r="P35" t="n">
-        <v>271.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10645,25 +10645,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>176.2252773581974</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
-        <v>142.1340339220183</v>
+        <v>180.1185623197441</v>
       </c>
       <c r="N36" t="n">
-        <v>131.3417120833333</v>
+        <v>170.9255890451739</v>
       </c>
       <c r="O36" t="n">
-        <v>182.5962444444444</v>
+        <v>182.180121406285</v>
       </c>
       <c r="P36" t="n">
-        <v>173.9744074143302</v>
+        <v>173.5582843761708</v>
       </c>
       <c r="Q36" t="n">
-        <v>179.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10733,7 +10733,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N37" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O37" t="n">
         <v>163.0416663658825</v>
@@ -10806,19 +10806,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L38" t="n">
-        <v>275.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M38" t="n">
-        <v>270.3462332272727</v>
+        <v>268.3307616249986</v>
       </c>
       <c r="N38" t="n">
-        <v>269.4130635965909</v>
+        <v>268.9969405584315</v>
       </c>
       <c r="O38" t="n">
-        <v>268.4820498055251</v>
+        <v>269.6820883835273</v>
       </c>
       <c r="P38" t="n">
-        <v>231.2329957552695</v>
+        <v>270.8168727171101</v>
       </c>
       <c r="Q38" t="n">
         <v>212.3149906599047</v>
@@ -10885,19 +10885,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>176.9382181637126</v>
+        <v>176.5389081776</v>
       </c>
       <c r="M39" t="n">
-        <v>142.1340339220183</v>
+        <v>181.7179108838589</v>
       </c>
       <c r="N39" t="n">
-        <v>171.3417120833333</v>
+        <v>170.9255890451739</v>
       </c>
       <c r="O39" t="n">
-        <v>182.5962444444444</v>
+        <v>182.180121406285</v>
       </c>
       <c r="P39" t="n">
-        <v>173.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
         <v>139.9817740860215</v>
@@ -10970,7 +10970,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N40" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O40" t="n">
         <v>163.0416663658825</v>
@@ -11043,19 +11043,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L41" t="n">
-        <v>275.7664149699872</v>
+        <v>275.3502919318278</v>
       </c>
       <c r="M41" t="n">
-        <v>270.3462332272727</v>
+        <v>269.9301101891133</v>
       </c>
       <c r="N41" t="n">
-        <v>269.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O41" t="n">
-        <v>268.4820498055251</v>
+        <v>269.6820883835273</v>
       </c>
       <c r="P41" t="n">
-        <v>231.2329957552695</v>
+        <v>269.2175241529953</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11125,19 +11125,19 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
-        <v>142.1340339220183</v>
+        <v>180.1185623197441</v>
       </c>
       <c r="N42" t="n">
-        <v>169.7255504671717</v>
+        <v>170.9255890451739</v>
       </c>
       <c r="O42" t="n">
-        <v>182.5962444444444</v>
+        <v>182.180121406285</v>
       </c>
       <c r="P42" t="n">
-        <v>173.9744074143302</v>
+        <v>173.5582843761708</v>
       </c>
       <c r="Q42" t="n">
-        <v>179.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11207,7 +11207,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N43" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O43" t="n">
         <v>163.0416663658825</v>
@@ -23932,25 +23932,25 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D20" t="n">
-        <v>319.451041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
-        <v>341.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
-        <v>366.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>375.302737515135</v>
+        <v>402.3772472563032</v>
       </c>
       <c r="H20" t="n">
-        <v>339.4748021157671</v>
+        <v>299.8909251539266</v>
       </c>
       <c r="I20" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J20" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -23971,7 +23971,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>149.8691179411497</v>
@@ -23989,13 +23989,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>349.240968717413</v>
+        <v>309.6570917555724</v>
       </c>
       <c r="X20" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.2379386560536</v>
+        <v>346.654061694213</v>
       </c>
     </row>
     <row r="21">
@@ -24011,22 +24011,22 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>147.4450655646388</v>
+        <v>112.5795867366496</v>
       </c>
       <c r="E21" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>109.8372123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>97.34351716321063</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>72.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I21" t="n">
-        <v>49.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
         <v>0.7465913262578567</v>
@@ -24056,19 +24056,19 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
-        <v>171.6831711038378</v>
+        <v>132.0992941419972</v>
       </c>
       <c r="T21" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>186.3575051191342</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>251.6949831609196</v>
+        <v>212.111106199079</v>
       </c>
       <c r="X21" t="n">
         <v>205.7729852034775</v>
@@ -24093,25 +24093,25 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E22" t="n">
-        <v>146.4339626465692</v>
+        <v>106.8500856847286</v>
       </c>
       <c r="F22" t="n">
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>158.8539539219727</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H22" t="n">
-        <v>122.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I22" t="n">
-        <v>115.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J22" t="n">
-        <v>53.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K22" t="n">
-        <v>22.26949182588285</v>
+        <v>12.29193946461858</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -24144,13 +24144,13 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V22" t="n">
-        <v>252.137643323828</v>
+        <v>212.5537663619874</v>
       </c>
       <c r="W22" t="n">
         <v>286.522998336591</v>
       </c>
       <c r="X22" t="n">
-        <v>225.7096553890372</v>
+        <v>186.1257784271966</v>
       </c>
       <c r="Y22" t="n">
         <v>218.5846533520948</v>
@@ -24181,13 +24181,13 @@
         <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
-        <v>339.4748021157671</v>
+        <v>316.5586126423905</v>
       </c>
       <c r="I23" t="n">
-        <v>210.4758895704059</v>
+        <v>170.8920126085653</v>
       </c>
       <c r="J23" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -24211,13 +24211,13 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>109.8691179411497</v>
+        <v>110.2852409793091</v>
       </c>
       <c r="S23" t="n">
-        <v>169.0200695862453</v>
+        <v>169.4361926244048</v>
       </c>
       <c r="T23" t="n">
-        <v>183.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U23" t="n">
         <v>251.3456529078365</v>
@@ -24226,7 +24226,7 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W23" t="n">
-        <v>314.008968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X23" t="n">
         <v>369.731100678469</v>
@@ -24242,7 +24242,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>166.5331836498673</v>
+        <v>126.9493066880268</v>
       </c>
       <c r="C24" t="n">
         <v>172.7084989883157</v>
@@ -24251,13 +24251,13 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
-        <v>117.6450804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>102.4780383352215</v>
       </c>
       <c r="H24" t="n">
         <v>112.2354442364965</v>
@@ -24299,19 +24299,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
-        <v>185.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
-        <v>197.5685871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>211.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>166.1891082416369</v>
       </c>
       <c r="Y24" t="n">
-        <v>205.6826957773044</v>
+        <v>166.0988188154638</v>
       </c>
     </row>
     <row r="25">
@@ -24336,7 +24336,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.9909793584588</v>
+        <v>128.4071023966182</v>
       </c>
       <c r="H25" t="n">
         <v>162.2271725074396</v>
@@ -24345,10 +24345,10 @@
         <v>155.4504749272583</v>
       </c>
       <c r="J25" t="n">
-        <v>93.35918011667277</v>
+        <v>66.06724261945077</v>
       </c>
       <c r="K25" t="n">
-        <v>15.85390712450328</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -24363,16 +24363,16 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q25" t="n">
-        <v>46.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>137.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S25" t="n">
-        <v>184.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T25" t="n">
         <v>227.9455894282815</v>
@@ -24390,7 +24390,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y25" t="n">
-        <v>218.5846533520948</v>
+        <v>179.0007763902542</v>
       </c>
     </row>
     <row r="26">
@@ -24415,10 +24415,10 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>375.302737515135</v>
+        <v>375.7188605532945</v>
       </c>
       <c r="H26" t="n">
-        <v>299.4748021157671</v>
+        <v>304.609323287778</v>
       </c>
       <c r="I26" t="n">
         <v>210.4758895704059</v>
@@ -24451,7 +24451,7 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
-        <v>169.0200695862453</v>
+        <v>169.4361926244048</v>
       </c>
       <c r="T26" t="n">
         <v>223.0958495641314</v>
@@ -24460,7 +24460,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
-        <v>292.5202584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W26" t="n">
         <v>349.240968717413</v>
@@ -24469,7 +24469,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>386.2379386560536</v>
+        <v>346.654061694213</v>
       </c>
     </row>
     <row r="27">
@@ -24479,7 +24479,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>166.5331836498673</v>
+        <v>131.6677048218782</v>
       </c>
       <c r="C27" t="n">
         <v>172.7084989883157</v>
@@ -24488,16 +24488,16 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>118.0612034935604</v>
       </c>
       <c r="F27" t="n">
-        <v>145.0692123933839</v>
+        <v>105.4853354315433</v>
       </c>
       <c r="G27" t="n">
-        <v>102.1115171632107</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H27" t="n">
-        <v>72.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I27" t="n">
         <v>89.39663285141508</v>
@@ -24539,16 +24539,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>192.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>251.6949831609196</v>
+        <v>212.111106199079</v>
       </c>
       <c r="X27" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>165.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="28">
@@ -24606,16 +24606,16 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
-        <v>168.1563659406834</v>
+        <v>137.7095144153289</v>
       </c>
       <c r="S28" t="n">
-        <v>184.0165980369723</v>
+        <v>184.4327210751317</v>
       </c>
       <c r="T28" t="n">
-        <v>187.9455894282815</v>
+        <v>188.3617124664409</v>
       </c>
       <c r="U28" t="n">
-        <v>246.3190293564909</v>
+        <v>276.3414769952266</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24637,22 +24637,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>382.7338416634806</v>
+        <v>343.14996470164</v>
       </c>
       <c r="C29" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D29" t="n">
-        <v>319.451041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E29" t="n">
-        <v>341.9303700722618</v>
+        <v>347.0648912442726</v>
       </c>
       <c r="F29" t="n">
-        <v>366.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>415.302737515135</v>
+        <v>375.7188605532945</v>
       </c>
       <c r="H29" t="n">
         <v>339.4748021157671</v>
@@ -24706,7 +24706,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>346.2379386560536</v>
+        <v>346.654061694213</v>
       </c>
     </row>
     <row r="30">
@@ -24716,7 +24716,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>126.5331836498673</v>
+        <v>131.6677048218782</v>
       </c>
       <c r="C30" t="n">
         <v>172.7084989883157</v>
@@ -24728,13 +24728,13 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
-        <v>145.0692123933839</v>
+        <v>105.4853354315433</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632106</v>
+        <v>97.75964020137005</v>
       </c>
       <c r="H30" t="n">
-        <v>112.2354442364965</v>
+        <v>72.65156727465587</v>
       </c>
       <c r="I30" t="n">
         <v>89.39663285141508</v>
@@ -24773,13 +24773,13 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>190.7093820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>192.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>211.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X30" t="n">
         <v>205.7729852034775</v>
@@ -24810,19 +24810,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>141.1234457478555</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H31" t="n">
-        <v>122.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I31" t="n">
         <v>155.4504749272583</v>
       </c>
       <c r="J31" t="n">
-        <v>53.35918011667277</v>
+        <v>53.77530315483219</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -24840,10 +24840,10 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q31" t="n">
-        <v>86.16204325169439</v>
+        <v>46.5781662898538</v>
       </c>
       <c r="R31" t="n">
-        <v>177.2933913771695</v>
+        <v>137.7095144153289</v>
       </c>
       <c r="S31" t="n">
         <v>224.0165980369723</v>
@@ -24861,7 +24861,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X31" t="n">
-        <v>225.7096553890372</v>
+        <v>215.7321030277729</v>
       </c>
       <c r="Y31" t="n">
         <v>218.5846533520948</v>
@@ -24874,10 +24874,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>382.7338416634806</v>
+        <v>357.8590620500362</v>
       </c>
       <c r="C32" t="n">
-        <v>365.2728917710076</v>
+        <v>325.689014809167</v>
       </c>
       <c r="D32" t="n">
         <v>354.683041620683</v>
@@ -24919,16 +24919,16 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>109.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>183.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
         <v>251.3456529078365</v>
@@ -24937,13 +24937,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
-        <v>349.240968717413</v>
+        <v>309.6570917555724</v>
       </c>
       <c r="X32" t="n">
-        <v>334.4991006784691</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
-        <v>346.2379386560536</v>
+        <v>346.654061694213</v>
       </c>
     </row>
     <row r="33">
@@ -24956,7 +24956,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>137.4764989883158</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
         <v>147.4450655646388</v>
@@ -25001,22 +25001,22 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>60.57395719080255</v>
       </c>
       <c r="S33" t="n">
-        <v>131.6831711038378</v>
+        <v>132.0992941419972</v>
       </c>
       <c r="T33" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>185.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
-        <v>232.8005871494253</v>
+        <v>193.2167101875847</v>
       </c>
       <c r="W33" t="n">
-        <v>211.6949831609196</v>
+        <v>216.8295043329304</v>
       </c>
       <c r="X33" t="n">
         <v>205.7729852034775</v>
@@ -25032,7 +25032,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>179.8319801819373</v>
+        <v>169.854427820673</v>
       </c>
       <c r="C34" t="n">
         <v>167.2468210986278</v>
@@ -25041,16 +25041,16 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E34" t="n">
-        <v>137.2969372100831</v>
+        <v>146.4339626465692</v>
       </c>
       <c r="F34" t="n">
-        <v>105.4210480229312</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>127.9909793584588</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H34" t="n">
-        <v>122.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I34" t="n">
         <v>155.4504749272583</v>
@@ -25095,13 +25095,13 @@
         <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
-        <v>286.522998336591</v>
+        <v>246.9391213747504</v>
       </c>
       <c r="X34" t="n">
-        <v>225.7096553890372</v>
+        <v>186.1257784271966</v>
       </c>
       <c r="Y34" t="n">
-        <v>218.5846533520948</v>
+        <v>179.0007763902542</v>
       </c>
     </row>
     <row r="35">
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>382.7338416634806</v>
+        <v>347.8683628354914</v>
       </c>
       <c r="C35" t="n">
-        <v>365.2728917710076</v>
+        <v>325.689014809167</v>
       </c>
       <c r="D35" t="n">
         <v>354.683041620683</v>
@@ -25123,16 +25123,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F35" t="n">
-        <v>406.8760457417114</v>
+        <v>367.2921687798708</v>
       </c>
       <c r="G35" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
-        <v>299.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I35" t="n">
-        <v>170.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J35" t="n">
         <v>11.94928935461252</v>
@@ -25156,13 +25156,13 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
-        <v>209.0200695862453</v>
+        <v>169.4361926244048</v>
       </c>
       <c r="T35" t="n">
         <v>223.0958495641314</v>
@@ -25174,10 +25174,10 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
-        <v>309.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X35" t="n">
-        <v>344.4897998930139</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y35" t="n">
         <v>386.2379386560536</v>
@@ -25190,13 +25190,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>131.6677048218782</v>
       </c>
       <c r="C36" t="n">
-        <v>137.4764989883158</v>
+        <v>133.1246220264752</v>
       </c>
       <c r="D36" t="n">
-        <v>147.4450655646388</v>
+        <v>107.8611886027982</v>
       </c>
       <c r="E36" t="n">
         <v>157.6450804554009</v>
@@ -25211,7 +25211,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I36" t="n">
-        <v>89.39663285141508</v>
+        <v>49.81275588957449</v>
       </c>
       <c r="J36" t="n">
         <v>0.7465913262578567</v>
@@ -25241,19 +25241,19 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>131.6831711038378</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>185.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>211.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X36" t="n">
         <v>205.7729852034775</v>
@@ -25311,19 +25311,19 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q37" t="n">
-        <v>46.16204325169439</v>
+        <v>76.18449089043011</v>
       </c>
       <c r="R37" t="n">
-        <v>137.2933913771695</v>
+        <v>137.7095144153289</v>
       </c>
       <c r="S37" t="n">
-        <v>184.0165980369723</v>
+        <v>184.4327210751317</v>
       </c>
       <c r="T37" t="n">
-        <v>221.5300047269019</v>
+        <v>188.3617124664409</v>
       </c>
       <c r="U37" t="n">
         <v>286.3190293564909</v>
@@ -25348,7 +25348,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>382.7338416634806</v>
+        <v>343.14996470164</v>
       </c>
       <c r="C38" t="n">
         <v>365.2728917710076</v>
@@ -25360,7 +25360,7 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
-        <v>406.8760457417114</v>
+        <v>382.001266128267</v>
       </c>
       <c r="G38" t="n">
         <v>415.302737515135</v>
@@ -25369,10 +25369,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I38" t="n">
-        <v>187.1931789250185</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25393,10 +25393,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>149.8691179411497</v>
+        <v>110.2852409793091</v>
       </c>
       <c r="S38" t="n">
         <v>209.0200695862453</v>
@@ -25405,19 +25405,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>211.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V38" t="n">
-        <v>287.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W38" t="n">
-        <v>309.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X38" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>386.2379386560536</v>
+        <v>346.654061694213</v>
       </c>
     </row>
     <row r="39">
@@ -25427,13 +25427,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>132.0477749761252</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>147.4450655646388</v>
+        <v>112.5795867366496</v>
       </c>
       <c r="E39" t="n">
         <v>157.6450804554009</v>
@@ -25451,7 +25451,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -25478,25 +25478,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>131.6831711038378</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>160.1647286948216</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
-        <v>232.8005871494253</v>
+        <v>193.2167101875847</v>
       </c>
       <c r="W39" t="n">
-        <v>251.6949831609196</v>
+        <v>212.111106199079</v>
       </c>
       <c r="X39" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>165.6826957773044</v>
+        <v>166.0988188154638</v>
       </c>
     </row>
     <row r="40">
@@ -25512,16 +25512,16 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D40" t="n">
-        <v>142.1998883168328</v>
+        <v>109.0315960563718</v>
       </c>
       <c r="E40" t="n">
-        <v>106.4339626465692</v>
+        <v>106.8500856847286</v>
       </c>
       <c r="F40" t="n">
-        <v>105.4210480229312</v>
+        <v>135.443495661667</v>
       </c>
       <c r="G40" t="n">
-        <v>127.9909793584588</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H40" t="n">
         <v>162.2271725074396</v>
@@ -25548,7 +25548,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q40" t="n">
         <v>86.16204325169439</v>
@@ -25560,7 +25560,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T40" t="n">
-        <v>227.9455894282815</v>
+        <v>188.3617124664409</v>
       </c>
       <c r="U40" t="n">
         <v>286.3190293564909</v>
@@ -25585,10 +25585,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>382.7338416634806</v>
+        <v>343.14996470164</v>
       </c>
       <c r="C41" t="n">
-        <v>325.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D41" t="n">
         <v>354.683041620683</v>
@@ -25597,13 +25597,13 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
-        <v>381.6347449562563</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>415.302737515135</v>
+        <v>375.7188605532945</v>
       </c>
       <c r="H41" t="n">
-        <v>339.4748021157671</v>
+        <v>299.8909251539266</v>
       </c>
       <c r="I41" t="n">
         <v>210.4758895704059</v>
@@ -25642,13 +25642,13 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U41" t="n">
-        <v>211.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>287.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>349.240968717413</v>
+        <v>324.3661891039686</v>
       </c>
       <c r="X41" t="n">
         <v>369.731100678469</v>
@@ -25664,10 +25664,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>126.5331836498673</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
-        <v>132.7084989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
         <v>147.4450655646388</v>
@@ -25682,10 +25682,10 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>72.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
-        <v>54.16463285141511</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
         <v>0.7465913262578567</v>
@@ -25712,22 +25712,22 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>100.1578341526431</v>
+        <v>60.57395719080255</v>
       </c>
       <c r="S42" t="n">
-        <v>171.6831711038378</v>
+        <v>132.0992941419972</v>
       </c>
       <c r="T42" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>186.3575051191342</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>251.6949831609196</v>
+        <v>216.8295043329304</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
@@ -25743,19 +25743,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>139.8319801819373</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C43" t="n">
         <v>167.2468210986278</v>
       </c>
       <c r="D43" t="n">
-        <v>139.4784475817263</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E43" t="n">
-        <v>106.4339626465692</v>
+        <v>121.8634658844537</v>
       </c>
       <c r="F43" t="n">
-        <v>105.4210480229312</v>
+        <v>105.8371710610907</v>
       </c>
       <c r="G43" t="n">
         <v>167.9909793584588</v>
@@ -25770,7 +25770,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K43" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -25785,7 +25785,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>86.16204325169439</v>
@@ -25803,7 +25803,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V43" t="n">
-        <v>252.137643323828</v>
+        <v>212.5537663619874</v>
       </c>
       <c r="W43" t="n">
         <v>286.522998336591</v>
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>367453.5983135027</v>
+        <v>367132.8408820864</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>367453.5983135024</v>
+        <v>367132.8408820863</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>367453.5983135027</v>
+        <v>367132.8408820865</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>367453.5983135027</v>
+        <v>367132.8408820865</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>367453.5983135026</v>
+        <v>367132.8408820865</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>367453.5983135026</v>
+        <v>367132.8408820865</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>367453.5983135026</v>
+        <v>367132.8408820864</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>367453.5983135027</v>
+        <v>367132.8408820865</v>
       </c>
     </row>
     <row r="16">
@@ -26264,46 +26264,46 @@
         <v>53753.7027657232</v>
       </c>
       <c r="C2" t="n">
-        <v>53753.70276572321</v>
+        <v>53753.7027657232</v>
       </c>
       <c r="D2" t="n">
-        <v>53753.70276572321</v>
+        <v>53753.7027657232</v>
       </c>
       <c r="E2" t="n">
-        <v>53753.70276572321</v>
+        <v>53753.7027657232</v>
       </c>
       <c r="F2" t="n">
         <v>53753.7027657232</v>
       </c>
       <c r="G2" t="n">
-        <v>53753.70276572321</v>
+        <v>53753.7027657232</v>
       </c>
       <c r="H2" t="n">
-        <v>59263.10091834213</v>
+        <v>59211.39971146602</v>
       </c>
       <c r="I2" t="n">
-        <v>59263.10091834213</v>
+        <v>59211.39971146602</v>
       </c>
       <c r="J2" t="n">
-        <v>59263.10091834212</v>
+        <v>59211.39971146598</v>
       </c>
       <c r="K2" t="n">
-        <v>59263.10091834213</v>
+        <v>59211.39971146598</v>
       </c>
       <c r="L2" t="n">
-        <v>59263.10091834213</v>
+        <v>59211.39971146601</v>
       </c>
       <c r="M2" t="n">
-        <v>59263.10091834213</v>
+        <v>59211.39971146601</v>
       </c>
       <c r="N2" t="n">
-        <v>59263.10091834213</v>
+        <v>59211.39971146601</v>
       </c>
       <c r="O2" t="n">
-        <v>59263.10091834213</v>
+        <v>59211.39971146602</v>
       </c>
       <c r="P2" t="n">
-        <v>53753.70276572321</v>
+        <v>53753.7027657232</v>
       </c>
     </row>
     <row r="3">
@@ -26331,7 +26331,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>10792.36</v>
+        <v>10680.08625919725</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10750.74055314464</v>
+        <v>10498.77007143031</v>
       </c>
       <c r="C4" t="n">
-        <v>10750.74055314464</v>
+        <v>10498.77007143031</v>
       </c>
       <c r="D4" t="n">
-        <v>10750.74055314464</v>
+        <v>10498.77007143031</v>
       </c>
       <c r="E4" t="n">
-        <v>10750.74055314464</v>
+        <v>10498.77007143031</v>
       </c>
       <c r="F4" t="n">
-        <v>10750.74055314464</v>
+        <v>10498.77007143031</v>
       </c>
       <c r="G4" t="n">
-        <v>10750.74055314464</v>
+        <v>10498.77007143031</v>
       </c>
       <c r="H4" t="n">
-        <v>11908.72037095864</v>
+        <v>11619.78080134547</v>
       </c>
       <c r="I4" t="n">
-        <v>11908.72037095864</v>
+        <v>11619.78080134547</v>
       </c>
       <c r="J4" t="n">
-        <v>11908.72037095864</v>
+        <v>11619.78080134547</v>
       </c>
       <c r="K4" t="n">
-        <v>11908.72037095864</v>
+        <v>11619.78080134547</v>
       </c>
       <c r="L4" t="n">
-        <v>11908.72037095864</v>
+        <v>11619.78080134547</v>
       </c>
       <c r="M4" t="n">
-        <v>11908.72037095864</v>
+        <v>11619.78080134547</v>
       </c>
       <c r="N4" t="n">
-        <v>11908.72037095864</v>
+        <v>11619.78080134547</v>
       </c>
       <c r="O4" t="n">
-        <v>11908.72037095864</v>
+        <v>11619.78080134547</v>
       </c>
       <c r="P4" t="n">
-        <v>10750.74055314464</v>
+        <v>10498.77007143031</v>
       </c>
     </row>
     <row r="5">
@@ -26435,28 +26435,28 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="I5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="J5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="K5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="L5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="M5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="N5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="O5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9375.362212578562</v>
+        <v>9627.332694292883</v>
       </c>
       <c r="C6" t="n">
-        <v>9375.36221257857</v>
+        <v>9627.332694292883</v>
       </c>
       <c r="D6" t="n">
-        <v>9375.36221257857</v>
+        <v>9627.332694292891</v>
       </c>
       <c r="E6" t="n">
-        <v>43002.96221257857</v>
+        <v>43254.93269429289</v>
       </c>
       <c r="F6" t="n">
-        <v>43002.96221257856</v>
+        <v>43254.93269429289</v>
       </c>
       <c r="G6" t="n">
-        <v>43002.96221257857</v>
+        <v>43254.93269429289</v>
       </c>
       <c r="H6" t="n">
-        <v>34130.02054738349</v>
+        <v>34504.8329316434</v>
       </c>
       <c r="I6" t="n">
-        <v>44922.38054738349</v>
+        <v>45184.91919084064</v>
       </c>
       <c r="J6" t="n">
-        <v>44922.38054738348</v>
+        <v>45184.9191908406</v>
       </c>
       <c r="K6" t="n">
-        <v>44922.38054738349</v>
+        <v>45184.9191908406</v>
       </c>
       <c r="L6" t="n">
-        <v>44922.38054738349</v>
+        <v>45184.91919084063</v>
       </c>
       <c r="M6" t="n">
-        <v>44922.38054738349</v>
+        <v>45184.91919084063</v>
       </c>
       <c r="N6" t="n">
-        <v>44922.38054738349</v>
+        <v>45184.91919084063</v>
       </c>
       <c r="O6" t="n">
-        <v>44922.38054738349</v>
+        <v>45184.91919084064</v>
       </c>
       <c r="P6" t="n">
-        <v>43002.96221257857</v>
+        <v>43254.93269429288</v>
       </c>
     </row>
   </sheetData>
@@ -26745,28 +26745,28 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="I4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="J4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="K4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="M4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="N4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,13 +26892,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26916,25 +26916,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,46 +26947,46 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27203,7 +27203,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
   </sheetData>
@@ -36036,19 +36036,19 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="M20" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="N20" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O20" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -36115,25 +36115,25 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36203,7 +36203,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N22" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O22" t="n">
         <v>24.58512791403967</v>
@@ -36276,19 +36276,19 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>40</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="M23" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="N23" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36352,25 +36352,25 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="M24" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36440,7 +36440,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N25" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O25" t="n">
         <v>24.58512791403967</v>
@@ -36510,19 +36510,19 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>40</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="L26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O26" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -36589,25 +36589,25 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P27" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36677,7 +36677,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N28" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O28" t="n">
         <v>24.58512791403967</v>
@@ -36747,19 +36747,19 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="L29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="N29" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O29" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -36826,25 +36826,25 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="L30" t="n">
-        <v>40</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="M30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36914,7 +36914,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N31" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O31" t="n">
         <v>24.58512791403967</v>
@@ -36984,22 +36984,22 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="L32" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>40</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P32" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37063,25 +37063,25 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="L33" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37151,7 +37151,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N34" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O34" t="n">
         <v>24.58512791403967</v>
@@ -37224,19 +37224,19 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="M35" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="N35" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="P35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37300,25 +37300,25 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O36" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P36" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37388,7 +37388,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N37" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O37" t="n">
         <v>24.58512791403967</v>
@@ -37461,19 +37461,19 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>40</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="N38" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O38" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37540,19 +37540,19 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>38.38383838383839</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="N39" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O39" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37625,7 +37625,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N40" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O40" t="n">
         <v>24.58512791403967</v>
@@ -37698,19 +37698,19 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="M41" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="N41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37780,19 +37780,19 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="N42" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O42" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P42" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37862,7 +37862,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N43" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O43" t="n">
         <v>24.58512791403967</v>
